--- a/branches/feature-careteam/StructureDefinition-riv-care-manager-careteam.xlsx
+++ b/branches/feature-careteam/StructureDefinition-riv-care-manager-careteam.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T08:56:04+00:00</t>
+    <t>2026-10-15T09:21:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -521,10 +521,10 @@
 </t>
   </si>
   <si>
-    <t>Kategori: fast kontakt</t>
-  </si>
-  <si>
-    <t>Anger att resursen beskriver en fast kontakt och skiljer den från andra användningar av CareTeam, till exempel team. Värdet är fast och är alltid koden fast-kontakt.</t>
+    <t>Type of team</t>
+  </si>
+  <si>
+    <t>Identifies what kind of team.  This is to support differentiation between multiple co-existing teams, such as care plan team, episode of care team, longitudinal care team.</t>
   </si>
   <si>
     <t>There may be multiple axis of categorization and one team may serve multiple purposes.</t>
@@ -541,13 +541,10 @@
 &lt;/valueCodeableConcept&gt;</t>
   </si>
   <si>
-    <t>example</t>
-  </si>
-  <si>
-    <t>Kategori av CareTeam.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/care-team-category</t>
+    <t>Typ av CareTeam enligt Ineras kodverk.</t>
+  </si>
+  <si>
+    <t>https://fhir.inera.se/ig/careteam/ValueSet/typ-av-careteam-vs</t>
   </si>
   <si>
     <t>FiveWs.class</t>
@@ -1093,6 +1090,9 @@
   </si>
   <si>
     <t>Används inte för fast kontakt.</t>
+  </si>
+  <si>
+    <t>example</t>
   </si>
   <si>
     <t>Indicates the reason for the care team.</t>
@@ -3395,13 +3395,13 @@
         <v>78</v>
       </c>
       <c r="X13" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="Y13" t="s" s="2">
         <v>167</v>
       </c>
-      <c r="Y13" t="s" s="2">
+      <c r="Z13" t="s" s="2">
         <v>168</v>
-      </c>
-      <c r="Z13" t="s" s="2">
-        <v>169</v>
       </c>
       <c r="AA13" t="s" s="2">
         <v>78</v>
@@ -3437,7 +3437,7 @@
         <v>78</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="AM13" t="s" s="2">
         <v>78</v>
@@ -3451,10 +3451,10 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3480,10 +3480,10 @@
         <v>90</v>
       </c>
       <c r="L14" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="M14" t="s" s="2">
         <v>172</v>
-      </c>
-      <c r="M14" t="s" s="2">
-        <v>173</v>
       </c>
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
@@ -3534,7 +3534,7 @@
         <v>78</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>79</v>
@@ -3543,19 +3543,19 @@
         <v>88</v>
       </c>
       <c r="AI14" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="AJ14" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK14" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL14" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM14" t="s" s="2">
         <v>175</v>
-      </c>
-      <c r="AJ14" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AK14" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL14" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM14" t="s" s="2">
-        <v>176</v>
       </c>
       <c r="AN14" t="s" s="2">
         <v>78</v>
@@ -3566,14 +3566,14 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
@@ -3595,13 +3595,13 @@
         <v>135</v>
       </c>
       <c r="L15" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="M15" t="s" s="2">
         <v>179</v>
       </c>
-      <c r="M15" t="s" s="2">
+      <c r="N15" t="s" s="2">
         <v>180</v>
-      </c>
-      <c r="N15" t="s" s="2">
-        <v>181</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
@@ -3639,19 +3639,19 @@
         <v>78</v>
       </c>
       <c r="AB15" t="s" s="2">
+        <v>181</v>
+      </c>
+      <c r="AC15" t="s" s="2">
         <v>182</v>
       </c>
-      <c r="AC15" t="s" s="2">
+      <c r="AD15" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE15" t="s" s="2">
         <v>183</v>
       </c>
-      <c r="AD15" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE15" t="s" s="2">
+      <c r="AF15" t="s" s="2">
         <v>184</v>
-      </c>
-      <c r="AF15" t="s" s="2">
-        <v>185</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>79</v>
@@ -3672,7 +3672,7 @@
         <v>78</v>
       </c>
       <c r="AM15" t="s" s="2">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="AN15" t="s" s="2">
         <v>78</v>
@@ -3683,10 +3683,10 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -3709,19 +3709,19 @@
         <v>89</v>
       </c>
       <c r="K16" t="s" s="2">
+        <v>186</v>
+      </c>
+      <c r="L16" t="s" s="2">
         <v>187</v>
       </c>
-      <c r="L16" t="s" s="2">
+      <c r="M16" t="s" s="2">
         <v>188</v>
       </c>
-      <c r="M16" t="s" s="2">
+      <c r="N16" t="s" s="2">
         <v>189</v>
       </c>
-      <c r="N16" t="s" s="2">
+      <c r="O16" t="s" s="2">
         <v>190</v>
-      </c>
-      <c r="O16" t="s" s="2">
-        <v>191</v>
       </c>
       <c r="P16" t="s" s="2">
         <v>78</v>
@@ -3770,7 +3770,7 @@
         <v>78</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>79</v>
@@ -3791,21 +3791,21 @@
         <v>78</v>
       </c>
       <c r="AM16" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="AN16" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO16" t="s" s="2">
         <v>193</v>
-      </c>
-      <c r="AN16" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AO16" t="s" s="2">
-        <v>194</v>
       </c>
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3831,10 +3831,10 @@
         <v>90</v>
       </c>
       <c r="L17" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="M17" t="s" s="2">
         <v>172</v>
-      </c>
-      <c r="M17" t="s" s="2">
-        <v>173</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -3885,7 +3885,7 @@
         <v>78</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>79</v>
@@ -3894,19 +3894,19 @@
         <v>88</v>
       </c>
       <c r="AI17" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="AJ17" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK17" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL17" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM17" t="s" s="2">
         <v>175</v>
-      </c>
-      <c r="AJ17" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AK17" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL17" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM17" t="s" s="2">
-        <v>176</v>
       </c>
       <c r="AN17" t="s" s="2">
         <v>78</v>
@@ -3917,14 +3917,14 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
@@ -3946,13 +3946,13 @@
         <v>135</v>
       </c>
       <c r="L18" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="M18" t="s" s="2">
         <v>179</v>
       </c>
-      <c r="M18" t="s" s="2">
+      <c r="N18" t="s" s="2">
         <v>180</v>
-      </c>
-      <c r="N18" t="s" s="2">
-        <v>181</v>
       </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
@@ -3990,19 +3990,19 @@
         <v>78</v>
       </c>
       <c r="AB18" t="s" s="2">
+        <v>181</v>
+      </c>
+      <c r="AC18" t="s" s="2">
         <v>182</v>
       </c>
-      <c r="AC18" t="s" s="2">
+      <c r="AD18" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE18" t="s" s="2">
         <v>183</v>
       </c>
-      <c r="AD18" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE18" t="s" s="2">
+      <c r="AF18" t="s" s="2">
         <v>184</v>
-      </c>
-      <c r="AF18" t="s" s="2">
-        <v>185</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>79</v>
@@ -4023,7 +4023,7 @@
         <v>78</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="AN18" t="s" s="2">
         <v>78</v>
@@ -4034,10 +4034,10 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4045,7 +4045,7 @@
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="G19" t="s" s="2">
         <v>88</v>
@@ -4063,16 +4063,16 @@
         <v>102</v>
       </c>
       <c r="L19" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="M19" t="s" s="2">
         <v>198</v>
       </c>
-      <c r="M19" t="s" s="2">
+      <c r="N19" t="s" s="2">
         <v>199</v>
       </c>
-      <c r="N19" t="s" s="2">
+      <c r="O19" t="s" s="2">
         <v>200</v>
-      </c>
-      <c r="O19" t="s" s="2">
-        <v>201</v>
       </c>
       <c r="P19" t="s" s="2">
         <v>78</v>
@@ -4121,7 +4121,7 @@
         <v>78</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>79</v>
@@ -4142,21 +4142,21 @@
         <v>78</v>
       </c>
       <c r="AM19" t="s" s="2">
+        <v>202</v>
+      </c>
+      <c r="AN19" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO19" t="s" s="2">
         <v>203</v>
-      </c>
-      <c r="AN19" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AO19" t="s" s="2">
-        <v>204</v>
       </c>
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4179,16 +4179,16 @@
         <v>89</v>
       </c>
       <c r="K20" t="s" s="2">
+        <v>205</v>
+      </c>
+      <c r="L20" t="s" s="2">
         <v>206</v>
       </c>
-      <c r="L20" t="s" s="2">
+      <c r="M20" t="s" s="2">
         <v>207</v>
       </c>
-      <c r="M20" t="s" s="2">
+      <c r="N20" t="s" s="2">
         <v>208</v>
-      </c>
-      <c r="N20" t="s" s="2">
-        <v>209</v>
       </c>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
@@ -4238,7 +4238,7 @@
         <v>78</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>79</v>
@@ -4259,21 +4259,21 @@
         <v>78</v>
       </c>
       <c r="AM20" t="s" s="2">
+        <v>210</v>
+      </c>
+      <c r="AN20" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO20" t="s" s="2">
         <v>211</v>
-      </c>
-      <c r="AN20" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AO20" t="s" s="2">
-        <v>212</v>
       </c>
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4281,7 +4281,7 @@
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="G21" t="s" s="2">
         <v>88</v>
@@ -4299,14 +4299,14 @@
         <v>108</v>
       </c>
       <c r="L21" t="s" s="2">
+        <v>213</v>
+      </c>
+      <c r="M21" t="s" s="2">
         <v>214</v>
-      </c>
-      <c r="M21" t="s" s="2">
-        <v>215</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" t="s" s="2">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="P21" t="s" s="2">
         <v>78</v>
@@ -4355,7 +4355,7 @@
         <v>78</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>79</v>
@@ -4364,7 +4364,7 @@
         <v>88</v>
       </c>
       <c r="AI21" t="s" s="2">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="AJ21" t="s" s="2">
         <v>100</v>
@@ -4376,21 +4376,21 @@
         <v>78</v>
       </c>
       <c r="AM21" t="s" s="2">
+        <v>218</v>
+      </c>
+      <c r="AN21" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO21" t="s" s="2">
         <v>219</v>
-      </c>
-      <c r="AN21" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AO21" t="s" s="2">
-        <v>220</v>
       </c>
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4413,17 +4413,17 @@
         <v>89</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="L22" t="s" s="2">
+        <v>221</v>
+      </c>
+      <c r="M22" t="s" s="2">
         <v>222</v>
-      </c>
-      <c r="M22" t="s" s="2">
-        <v>223</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" t="s" s="2">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>78</v>
@@ -4472,7 +4472,7 @@
         <v>78</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>79</v>
@@ -4481,7 +4481,7 @@
         <v>88</v>
       </c>
       <c r="AI22" t="s" s="2">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="AJ22" t="s" s="2">
         <v>100</v>
@@ -4493,21 +4493,21 @@
         <v>78</v>
       </c>
       <c r="AM22" t="s" s="2">
+        <v>225</v>
+      </c>
+      <c r="AN22" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO22" t="s" s="2">
         <v>226</v>
-      </c>
-      <c r="AN22" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AO22" t="s" s="2">
-        <v>227</v>
       </c>
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4530,19 +4530,19 @@
         <v>89</v>
       </c>
       <c r="K23" t="s" s="2">
+        <v>228</v>
+      </c>
+      <c r="L23" t="s" s="2">
         <v>229</v>
       </c>
-      <c r="L23" t="s" s="2">
+      <c r="M23" t="s" s="2">
         <v>230</v>
       </c>
-      <c r="M23" t="s" s="2">
+      <c r="N23" t="s" s="2">
         <v>231</v>
       </c>
-      <c r="N23" t="s" s="2">
+      <c r="O23" t="s" s="2">
         <v>232</v>
-      </c>
-      <c r="O23" t="s" s="2">
-        <v>233</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>78</v>
@@ -4591,7 +4591,7 @@
         <v>78</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>79</v>
@@ -4612,21 +4612,21 @@
         <v>78</v>
       </c>
       <c r="AM23" t="s" s="2">
+        <v>234</v>
+      </c>
+      <c r="AN23" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO23" t="s" s="2">
         <v>235</v>
-      </c>
-      <c r="AN23" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AO23" t="s" s="2">
-        <v>236</v>
       </c>
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4649,19 +4649,19 @@
         <v>89</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="L24" t="s" s="2">
+        <v>237</v>
+      </c>
+      <c r="M24" t="s" s="2">
         <v>238</v>
       </c>
-      <c r="M24" t="s" s="2">
+      <c r="N24" t="s" s="2">
         <v>239</v>
       </c>
-      <c r="N24" t="s" s="2">
+      <c r="O24" t="s" s="2">
         <v>240</v>
-      </c>
-      <c r="O24" t="s" s="2">
-        <v>241</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>78</v>
@@ -4710,7 +4710,7 @@
         <v>78</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>79</v>
@@ -4731,21 +4731,21 @@
         <v>78</v>
       </c>
       <c r="AM24" t="s" s="2">
+        <v>242</v>
+      </c>
+      <c r="AN24" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO24" t="s" s="2">
         <v>243</v>
-      </c>
-      <c r="AN24" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AO24" t="s" s="2">
-        <v>244</v>
       </c>
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4768,16 +4768,16 @@
         <v>89</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="L25" t="s" s="2">
+        <v>245</v>
+      </c>
+      <c r="M25" t="s" s="2">
         <v>246</v>
       </c>
-      <c r="M25" t="s" s="2">
+      <c r="N25" t="s" s="2">
         <v>247</v>
-      </c>
-      <c r="N25" t="s" s="2">
-        <v>248</v>
       </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
@@ -4827,7 +4827,7 @@
         <v>78</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>79</v>
@@ -4851,7 +4851,7 @@
         <v>78</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="AO25" t="s" s="2">
         <v>78</v>
@@ -4859,14 +4859,14 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
@@ -4885,19 +4885,19 @@
         <v>89</v>
       </c>
       <c r="K26" t="s" s="2">
+        <v>251</v>
+      </c>
+      <c r="L26" t="s" s="2">
         <v>252</v>
       </c>
-      <c r="L26" t="s" s="2">
+      <c r="M26" t="s" s="2">
         <v>253</v>
       </c>
-      <c r="M26" t="s" s="2">
+      <c r="N26" t="s" s="2">
         <v>254</v>
       </c>
-      <c r="N26" t="s" s="2">
+      <c r="O26" t="s" s="2">
         <v>255</v>
-      </c>
-      <c r="O26" t="s" s="2">
-        <v>256</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>78</v>
@@ -4946,7 +4946,7 @@
         <v>78</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>79</v>
@@ -4961,10 +4961,10 @@
         <v>100</v>
       </c>
       <c r="AK26" t="s" s="2">
+        <v>256</v>
+      </c>
+      <c r="AL26" t="s" s="2">
         <v>257</v>
-      </c>
-      <c r="AL26" t="s" s="2">
-        <v>258</v>
       </c>
       <c r="AM26" t="s" s="2">
         <v>78</v>
@@ -4978,10 +4978,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5004,17 +5004,17 @@
         <v>89</v>
       </c>
       <c r="K27" t="s" s="2">
+        <v>259</v>
+      </c>
+      <c r="L27" t="s" s="2">
         <v>260</v>
       </c>
-      <c r="L27" t="s" s="2">
+      <c r="M27" t="s" s="2">
         <v>261</v>
-      </c>
-      <c r="M27" t="s" s="2">
-        <v>262</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" t="s" s="2">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>78</v>
@@ -5063,7 +5063,7 @@
         <v>78</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>79</v>
@@ -5081,7 +5081,7 @@
         <v>78</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="AM27" t="s" s="2">
         <v>78</v>
@@ -5095,10 +5095,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5124,10 +5124,10 @@
         <v>90</v>
       </c>
       <c r="L28" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="M28" t="s" s="2">
         <v>172</v>
-      </c>
-      <c r="M28" t="s" s="2">
-        <v>173</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -5178,7 +5178,7 @@
         <v>78</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>79</v>
@@ -5187,19 +5187,19 @@
         <v>88</v>
       </c>
       <c r="AI28" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="AJ28" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK28" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL28" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM28" t="s" s="2">
         <v>175</v>
-      </c>
-      <c r="AJ28" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AK28" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL28" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM28" t="s" s="2">
-        <v>176</v>
       </c>
       <c r="AN28" t="s" s="2">
         <v>78</v>
@@ -5210,14 +5210,14 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
@@ -5239,13 +5239,13 @@
         <v>135</v>
       </c>
       <c r="L29" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="M29" t="s" s="2">
         <v>179</v>
       </c>
-      <c r="M29" t="s" s="2">
+      <c r="N29" t="s" s="2">
         <v>180</v>
-      </c>
-      <c r="N29" t="s" s="2">
-        <v>181</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -5283,19 +5283,19 @@
         <v>78</v>
       </c>
       <c r="AB29" t="s" s="2">
+        <v>181</v>
+      </c>
+      <c r="AC29" t="s" s="2">
         <v>182</v>
       </c>
-      <c r="AC29" t="s" s="2">
+      <c r="AD29" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE29" t="s" s="2">
         <v>183</v>
       </c>
-      <c r="AD29" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE29" t="s" s="2">
+      <c r="AF29" t="s" s="2">
         <v>184</v>
-      </c>
-      <c r="AF29" t="s" s="2">
-        <v>185</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>79</v>
@@ -5316,7 +5316,7 @@
         <v>78</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="AN29" t="s" s="2">
         <v>78</v>
@@ -5327,10 +5327,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5353,16 +5353,16 @@
         <v>89</v>
       </c>
       <c r="K30" t="s" s="2">
+        <v>267</v>
+      </c>
+      <c r="L30" t="s" s="2">
         <v>268</v>
       </c>
-      <c r="L30" t="s" s="2">
+      <c r="M30" t="s" s="2">
         <v>269</v>
       </c>
-      <c r="M30" t="s" s="2">
+      <c r="N30" t="s" s="2">
         <v>270</v>
-      </c>
-      <c r="N30" t="s" s="2">
-        <v>271</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -5412,7 +5412,7 @@
         <v>78</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>79</v>
@@ -5421,33 +5421,33 @@
         <v>88</v>
       </c>
       <c r="AI30" t="s" s="2">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="AJ30" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AK30" t="s" s="2">
+        <v>273</v>
+      </c>
+      <c r="AL30" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM30" t="s" s="2">
         <v>274</v>
       </c>
-      <c r="AL30" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM30" t="s" s="2">
+      <c r="AN30" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO30" t="s" s="2">
         <v>275</v>
-      </c>
-      <c r="AN30" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AO30" t="s" s="2">
-        <v>276</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5470,68 +5470,68 @@
         <v>89</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="L31" t="s" s="2">
+        <v>277</v>
+      </c>
+      <c r="M31" t="s" s="2">
         <v>278</v>
       </c>
-      <c r="M31" t="s" s="2">
+      <c r="N31" t="s" s="2">
         <v>279</v>
-      </c>
-      <c r="N31" t="s" s="2">
-        <v>280</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
         <v>78</v>
       </c>
       <c r="Q31" t="s" s="2">
+        <v>280</v>
+      </c>
+      <c r="R31" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S31" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T31" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U31" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V31" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W31" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X31" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y31" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z31" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA31" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB31" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC31" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD31" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE31" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF31" t="s" s="2">
         <v>281</v>
-      </c>
-      <c r="R31" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S31" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T31" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U31" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V31" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W31" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X31" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y31" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z31" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA31" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB31" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC31" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD31" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE31" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF31" t="s" s="2">
-        <v>282</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>79</v>
@@ -5540,33 +5540,33 @@
         <v>88</v>
       </c>
       <c r="AI31" t="s" s="2">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="AJ31" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AK31" t="s" s="2">
+        <v>282</v>
+      </c>
+      <c r="AL31" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM31" t="s" s="2">
         <v>283</v>
       </c>
-      <c r="AL31" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM31" t="s" s="2">
+      <c r="AN31" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO31" t="s" s="2">
         <v>284</v>
-      </c>
-      <c r="AN31" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AO31" t="s" s="2">
-        <v>285</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5589,13 +5589,13 @@
         <v>78</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="L32" t="s" s="2">
         <v>9</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -5646,7 +5646,7 @@
         <v>78</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>79</v>
@@ -5658,30 +5658,30 @@
         <v>78</v>
       </c>
       <c r="AJ32" t="s" s="2">
+        <v>288</v>
+      </c>
+      <c r="AK32" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL32" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM32" t="s" s="2">
         <v>289</v>
       </c>
-      <c r="AK32" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL32" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM32" t="s" s="2">
+      <c r="AN32" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO32" t="s" s="2">
         <v>290</v>
-      </c>
-      <c r="AN32" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AO32" t="s" s="2">
-        <v>291</v>
       </c>
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5704,13 +5704,13 @@
         <v>78</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="L33" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="M33" t="s" s="2">
         <v>172</v>
-      </c>
-      <c r="M33" t="s" s="2">
-        <v>173</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -5761,7 +5761,7 @@
         <v>78</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>79</v>
@@ -5770,19 +5770,19 @@
         <v>88</v>
       </c>
       <c r="AI33" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="AJ33" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK33" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL33" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM33" t="s" s="2">
         <v>175</v>
-      </c>
-      <c r="AJ33" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AK33" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL33" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM33" t="s" s="2">
-        <v>176</v>
       </c>
       <c r="AN33" t="s" s="2">
         <v>78</v>
@@ -5793,10 +5793,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5822,10 +5822,10 @@
         <v>135</v>
       </c>
       <c r="L34" t="s" s="2">
+        <v>293</v>
+      </c>
+      <c r="M34" t="s" s="2">
         <v>294</v>
-      </c>
-      <c r="M34" t="s" s="2">
-        <v>295</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -5864,17 +5864,17 @@
         <v>78</v>
       </c>
       <c r="AB34" t="s" s="2">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="AC34" s="2"/>
       <c r="AD34" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE34" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="AF34" t="s" s="2">
         <v>184</v>
-      </c>
-      <c r="AF34" t="s" s="2">
-        <v>185</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>79</v>
@@ -5906,13 +5906,13 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
+        <v>295</v>
+      </c>
+      <c r="B35" t="s" s="2">
+        <v>292</v>
+      </c>
+      <c r="C35" t="s" s="2">
         <v>296</v>
-      </c>
-      <c r="B35" t="s" s="2">
-        <v>293</v>
-      </c>
-      <c r="C35" t="s" s="2">
-        <v>297</v>
       </c>
       <c r="D35" t="s" s="2">
         <v>78</v>
@@ -5934,13 +5934,13 @@
         <v>78</v>
       </c>
       <c r="K35" t="s" s="2">
+        <v>297</v>
+      </c>
+      <c r="L35" t="s" s="2">
         <v>298</v>
       </c>
-      <c r="L35" t="s" s="2">
+      <c r="M35" t="s" s="2">
         <v>299</v>
-      </c>
-      <c r="M35" t="s" s="2">
-        <v>300</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -5991,7 +5991,7 @@
         <v>78</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>79</v>
@@ -6023,14 +6023,14 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
@@ -6052,16 +6052,16 @@
         <v>135</v>
       </c>
       <c r="L36" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="M36" t="s" s="2">
         <v>303</v>
       </c>
-      <c r="M36" t="s" s="2">
+      <c r="N36" t="s" s="2">
+        <v>180</v>
+      </c>
+      <c r="O36" t="s" s="2">
         <v>304</v>
-      </c>
-      <c r="N36" t="s" s="2">
-        <v>181</v>
-      </c>
-      <c r="O36" t="s" s="2">
-        <v>305</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>78</v>
@@ -6110,7 +6110,7 @@
         <v>78</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>79</v>
@@ -6142,10 +6142,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6171,13 +6171,13 @@
         <v>161</v>
       </c>
       <c r="L37" t="s" s="2">
+        <v>307</v>
+      </c>
+      <c r="M37" t="s" s="2">
         <v>308</v>
       </c>
-      <c r="M37" t="s" s="2">
+      <c r="N37" t="s" s="2">
         <v>309</v>
-      </c>
-      <c r="N37" t="s" s="2">
-        <v>310</v>
       </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
@@ -6206,11 +6206,11 @@
         <v>112</v>
       </c>
       <c r="Y37" t="s" s="2">
+        <v>310</v>
+      </c>
+      <c r="Z37" t="s" s="2">
         <v>311</v>
       </c>
-      <c r="Z37" t="s" s="2">
-        <v>312</v>
-      </c>
       <c r="AA37" t="s" s="2">
         <v>78</v>
       </c>
@@ -6227,7 +6227,7 @@
         <v>78</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>79</v>
@@ -6236,33 +6236,33 @@
         <v>88</v>
       </c>
       <c r="AI37" t="s" s="2">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="AJ37" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AK37" t="s" s="2">
+        <v>313</v>
+      </c>
+      <c r="AL37" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM37" t="s" s="2">
         <v>314</v>
       </c>
-      <c r="AL37" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM37" t="s" s="2">
+      <c r="AN37" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO37" t="s" s="2">
         <v>315</v>
-      </c>
-      <c r="AN37" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AO37" t="s" s="2">
-        <v>316</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6285,16 +6285,16 @@
         <v>89</v>
       </c>
       <c r="K38" t="s" s="2">
+        <v>317</v>
+      </c>
+      <c r="L38" t="s" s="2">
         <v>318</v>
       </c>
-      <c r="L38" t="s" s="2">
+      <c r="M38" t="s" s="2">
         <v>319</v>
       </c>
-      <c r="M38" t="s" s="2">
+      <c r="N38" t="s" s="2">
         <v>320</v>
-      </c>
-      <c r="N38" t="s" s="2">
-        <v>321</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -6344,7 +6344,7 @@
         <v>78</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>79</v>
@@ -6353,33 +6353,33 @@
         <v>88</v>
       </c>
       <c r="AI38" t="s" s="2">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="AJ38" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AK38" t="s" s="2">
+        <v>322</v>
+      </c>
+      <c r="AL38" t="s" s="2">
         <v>323</v>
       </c>
-      <c r="AL38" t="s" s="2">
+      <c r="AM38" t="s" s="2">
         <v>324</v>
       </c>
-      <c r="AM38" t="s" s="2">
+      <c r="AN38" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO38" t="s" s="2">
         <v>325</v>
-      </c>
-      <c r="AN38" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AO38" t="s" s="2">
-        <v>326</v>
       </c>
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6402,17 +6402,17 @@
         <v>89</v>
       </c>
       <c r="K39" t="s" s="2">
+        <v>327</v>
+      </c>
+      <c r="L39" t="s" s="2">
         <v>328</v>
       </c>
-      <c r="L39" t="s" s="2">
+      <c r="M39" t="s" s="2">
         <v>329</v>
-      </c>
-      <c r="M39" t="s" s="2">
-        <v>330</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" t="s" s="2">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>78</v>
@@ -6461,7 +6461,7 @@
         <v>78</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>79</v>
@@ -6470,7 +6470,7 @@
         <v>88</v>
       </c>
       <c r="AI39" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="AJ39" t="s" s="2">
         <v>100</v>
@@ -6493,10 +6493,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6519,19 +6519,19 @@
         <v>78</v>
       </c>
       <c r="K40" t="s" s="2">
+        <v>333</v>
+      </c>
+      <c r="L40" t="s" s="2">
         <v>334</v>
       </c>
-      <c r="L40" t="s" s="2">
+      <c r="M40" t="s" s="2">
         <v>335</v>
       </c>
-      <c r="M40" t="s" s="2">
+      <c r="N40" t="s" s="2">
         <v>336</v>
       </c>
-      <c r="N40" t="s" s="2">
+      <c r="O40" t="s" s="2">
         <v>337</v>
-      </c>
-      <c r="O40" t="s" s="2">
-        <v>338</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>78</v>
@@ -6580,7 +6580,7 @@
         <v>78</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>79</v>
@@ -6612,10 +6612,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6638,13 +6638,13 @@
         <v>78</v>
       </c>
       <c r="K41" t="s" s="2">
+        <v>339</v>
+      </c>
+      <c r="L41" t="s" s="2">
         <v>340</v>
       </c>
-      <c r="L41" t="s" s="2">
+      <c r="M41" t="s" s="2">
         <v>341</v>
-      </c>
-      <c r="M41" t="s" s="2">
-        <v>342</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -6671,7 +6671,7 @@
         <v>78</v>
       </c>
       <c r="X41" t="s" s="2">
-        <v>167</v>
+        <v>342</v>
       </c>
       <c r="Y41" t="s" s="2">
         <v>343</v>
@@ -6695,7 +6695,7 @@
         <v>78</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>79</v>
@@ -6753,13 +6753,13 @@
         <v>89</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="L42" t="s" s="2">
         <v>347</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" t="s" s="2">
@@ -6990,10 +6990,10 @@
         <v>90</v>
       </c>
       <c r="L44" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="M44" t="s" s="2">
         <v>172</v>
-      </c>
-      <c r="M44" t="s" s="2">
-        <v>173</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -7044,7 +7044,7 @@
         <v>78</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>79</v>
@@ -7053,19 +7053,19 @@
         <v>88</v>
       </c>
       <c r="AI44" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="AJ44" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK44" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL44" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM44" t="s" s="2">
         <v>175</v>
-      </c>
-      <c r="AJ44" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AK44" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL44" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM44" t="s" s="2">
-        <v>176</v>
       </c>
       <c r="AN44" t="s" s="2">
         <v>78</v>
@@ -7083,7 +7083,7 @@
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
@@ -7105,13 +7105,13 @@
         <v>135</v>
       </c>
       <c r="L45" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="M45" t="s" s="2">
         <v>179</v>
       </c>
-      <c r="M45" t="s" s="2">
+      <c r="N45" t="s" s="2">
         <v>180</v>
-      </c>
-      <c r="N45" t="s" s="2">
-        <v>181</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
@@ -7149,19 +7149,19 @@
         <v>78</v>
       </c>
       <c r="AB45" t="s" s="2">
+        <v>181</v>
+      </c>
+      <c r="AC45" t="s" s="2">
         <v>182</v>
       </c>
-      <c r="AC45" t="s" s="2">
+      <c r="AD45" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE45" t="s" s="2">
         <v>183</v>
       </c>
-      <c r="AD45" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE45" t="s" s="2">
+      <c r="AF45" t="s" s="2">
         <v>184</v>
-      </c>
-      <c r="AF45" t="s" s="2">
-        <v>185</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>79</v>
@@ -7182,7 +7182,7 @@
         <v>78</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="AN45" t="s" s="2">
         <v>78</v>
@@ -7278,7 +7278,7 @@
         <v>78</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>79</v>
@@ -7339,10 +7339,10 @@
         <v>90</v>
       </c>
       <c r="L47" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="M47" t="s" s="2">
         <v>172</v>
-      </c>
-      <c r="M47" t="s" s="2">
-        <v>173</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -7393,7 +7393,7 @@
         <v>78</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>79</v>
@@ -7402,19 +7402,19 @@
         <v>88</v>
       </c>
       <c r="AI47" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="AJ47" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK47" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL47" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM47" t="s" s="2">
         <v>175</v>
-      </c>
-      <c r="AJ47" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AK47" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL47" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM47" t="s" s="2">
-        <v>176</v>
       </c>
       <c r="AN47" t="s" s="2">
         <v>78</v>
@@ -7454,10 +7454,10 @@
         <v>135</v>
       </c>
       <c r="L48" t="s" s="2">
+        <v>293</v>
+      </c>
+      <c r="M48" t="s" s="2">
         <v>294</v>
-      </c>
-      <c r="M48" t="s" s="2">
-        <v>295</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -7496,19 +7496,19 @@
         <v>78</v>
       </c>
       <c r="AB48" t="s" s="2">
+        <v>181</v>
+      </c>
+      <c r="AC48" t="s" s="2">
         <v>182</v>
       </c>
-      <c r="AC48" t="s" s="2">
+      <c r="AD48" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE48" t="s" s="2">
         <v>183</v>
       </c>
-      <c r="AD48" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE48" t="s" s="2">
+      <c r="AF48" t="s" s="2">
         <v>184</v>
-      </c>
-      <c r="AF48" t="s" s="2">
-        <v>185</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>79</v>
@@ -7801,10 +7801,10 @@
         <v>90</v>
       </c>
       <c r="L51" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="M51" t="s" s="2">
         <v>172</v>
-      </c>
-      <c r="M51" t="s" s="2">
-        <v>173</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -7855,7 +7855,7 @@
         <v>78</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>79</v>
@@ -7864,19 +7864,19 @@
         <v>88</v>
       </c>
       <c r="AI51" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="AJ51" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK51" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL51" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM51" t="s" s="2">
         <v>175</v>
-      </c>
-      <c r="AJ51" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AK51" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL51" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM51" t="s" s="2">
-        <v>176</v>
       </c>
       <c r="AN51" t="s" s="2">
         <v>78</v>
@@ -7894,7 +7894,7 @@
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
@@ -7916,13 +7916,13 @@
         <v>135</v>
       </c>
       <c r="L52" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="M52" t="s" s="2">
         <v>179</v>
       </c>
-      <c r="M52" t="s" s="2">
+      <c r="N52" t="s" s="2">
         <v>180</v>
-      </c>
-      <c r="N52" t="s" s="2">
-        <v>181</v>
       </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
@@ -7960,19 +7960,19 @@
         <v>78</v>
       </c>
       <c r="AB52" t="s" s="2">
+        <v>181</v>
+      </c>
+      <c r="AC52" t="s" s="2">
         <v>182</v>
       </c>
-      <c r="AC52" t="s" s="2">
+      <c r="AD52" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE52" t="s" s="2">
         <v>183</v>
       </c>
-      <c r="AD52" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE52" t="s" s="2">
+      <c r="AF52" t="s" s="2">
         <v>184</v>
-      </c>
-      <c r="AF52" t="s" s="2">
-        <v>185</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>79</v>
@@ -7993,7 +7993,7 @@
         <v>78</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="AN52" t="s" s="2">
         <v>78</v>
@@ -8147,13 +8147,13 @@
         <v>78</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="L54" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="M54" t="s" s="2">
         <v>172</v>
-      </c>
-      <c r="M54" t="s" s="2">
-        <v>173</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -8204,7 +8204,7 @@
         <v>78</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>79</v>
@@ -8213,19 +8213,19 @@
         <v>88</v>
       </c>
       <c r="AI54" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="AJ54" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK54" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL54" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM54" t="s" s="2">
         <v>175</v>
-      </c>
-      <c r="AJ54" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AK54" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL54" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM54" t="s" s="2">
-        <v>176</v>
       </c>
       <c r="AN54" t="s" s="2">
         <v>78</v>
@@ -8243,7 +8243,7 @@
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
@@ -8265,13 +8265,13 @@
         <v>135</v>
       </c>
       <c r="L55" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="M55" t="s" s="2">
         <v>179</v>
       </c>
-      <c r="M55" t="s" s="2">
+      <c r="N55" t="s" s="2">
         <v>180</v>
-      </c>
-      <c r="N55" t="s" s="2">
-        <v>181</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -8309,19 +8309,19 @@
         <v>78</v>
       </c>
       <c r="AB55" t="s" s="2">
+        <v>181</v>
+      </c>
+      <c r="AC55" t="s" s="2">
         <v>182</v>
       </c>
-      <c r="AC55" t="s" s="2">
+      <c r="AD55" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE55" t="s" s="2">
         <v>183</v>
       </c>
-      <c r="AD55" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE55" t="s" s="2">
+      <c r="AF55" t="s" s="2">
         <v>184</v>
-      </c>
-      <c r="AF55" t="s" s="2">
-        <v>185</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>79</v>
@@ -8342,7 +8342,7 @@
         <v>78</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="AN55" t="s" s="2">
         <v>78</v>
@@ -8496,7 +8496,7 @@
         <v>89</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="L57" t="s" s="2">
         <v>406</v>
@@ -8968,13 +8968,13 @@
         <v>78</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="L61" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="M61" t="s" s="2">
         <v>172</v>
-      </c>
-      <c r="M61" t="s" s="2">
-        <v>173</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -9025,7 +9025,7 @@
         <v>78</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>79</v>
@@ -9034,19 +9034,19 @@
         <v>88</v>
       </c>
       <c r="AI61" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="AJ61" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK61" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL61" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM61" t="s" s="2">
         <v>175</v>
-      </c>
-      <c r="AJ61" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AK61" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL61" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM61" t="s" s="2">
-        <v>176</v>
       </c>
       <c r="AN61" t="s" s="2">
         <v>78</v>
@@ -9064,7 +9064,7 @@
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
@@ -9086,13 +9086,13 @@
         <v>135</v>
       </c>
       <c r="L62" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="M62" t="s" s="2">
         <v>179</v>
       </c>
-      <c r="M62" t="s" s="2">
+      <c r="N62" t="s" s="2">
         <v>180</v>
-      </c>
-      <c r="N62" t="s" s="2">
-        <v>181</v>
       </c>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
@@ -9130,19 +9130,19 @@
         <v>78</v>
       </c>
       <c r="AB62" t="s" s="2">
+        <v>181</v>
+      </c>
+      <c r="AC62" t="s" s="2">
         <v>182</v>
       </c>
-      <c r="AC62" t="s" s="2">
+      <c r="AD62" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE62" t="s" s="2">
         <v>183</v>
       </c>
-      <c r="AD62" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE62" t="s" s="2">
+      <c r="AF62" t="s" s="2">
         <v>184</v>
-      </c>
-      <c r="AF62" t="s" s="2">
-        <v>185</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>79</v>
@@ -9163,7 +9163,7 @@
         <v>78</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="AN62" t="s" s="2">
         <v>78</v>
@@ -9200,7 +9200,7 @@
         <v>89</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="L63" t="s" s="2">
         <v>439</v>
@@ -9319,7 +9319,7 @@
         <v>89</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="L64" t="s" s="2">
         <v>446</v>
@@ -9551,7 +9551,7 @@
         <v>89</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="L66" t="s" s="2">
         <v>461</v>
@@ -9869,13 +9869,13 @@
         <v>78</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="AN68" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AO68" t="s" s="2">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="69" hidden="true">
@@ -9906,7 +9906,7 @@
         <v>89</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="L69" t="s" s="2">
         <v>486</v>

--- a/branches/feature-careteam/StructureDefinition-riv-care-manager-careteam.xlsx
+++ b/branches/feature-careteam/StructureDefinition-riv-care-manager-careteam.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2624" uniqueCount="495">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2624" uniqueCount="497">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T09:21:11+00:00</t>
+    <t>2026-10-15T12:03:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -988,6 +988,9 @@
     <t>Roles may sometimes be inferred by type of Practitioner.  These are relationships that hold only within the context of the care team.  General relationships should be handled as properties of the Patient resource directly.  If a participant has multiple roles within the team, then there should be multiple participants.</t>
   </si>
   <si>
+    <t>extensible</t>
+  </si>
+  <si>
     <t>Typ av fast kontakt.</t>
   </si>
   <si>
@@ -996,6 +999,10 @@
   <si>
     <t xml:space="preserve">ctm-2
 </t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+fast-kontakt-typ-kod-eller-text:Typ av fast kontakt ska anges med kod från kodverket Typ av fast kontakt, med text eller med båda. Koder från andra kodverk får inte användas. {(coding.exists() or text.exists()) and coding.all(system = 'https://fhir.inera.se/ig/careteam/CodeSystem/&lt;id&gt;')}</t>
   </si>
   <si>
     <t>Fast kontakt.typ</t>
@@ -6203,13 +6210,13 @@
         <v>78</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>112</v>
+        <v>310</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="Z37" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>78</v>
@@ -6236,33 +6243,33 @@
         <v>88</v>
       </c>
       <c r="AI37" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>100</v>
+        <v>314</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="AL37" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="AN37" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AO37" t="s" s="2">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6285,16 +6292,16 @@
         <v>89</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -6344,7 +6351,7 @@
         <v>78</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>79</v>
@@ -6353,33 +6360,33 @@
         <v>88</v>
       </c>
       <c r="AI38" t="s" s="2">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="AJ38" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="AN38" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>325</v>
+        <v>327</v>
       </c>
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6402,17 +6409,17 @@
         <v>89</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" t="s" s="2">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>78</v>
@@ -6461,7 +6468,7 @@
         <v>78</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>79</v>
@@ -6470,7 +6477,7 @@
         <v>88</v>
       </c>
       <c r="AI39" t="s" s="2">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="AJ39" t="s" s="2">
         <v>100</v>
@@ -6493,10 +6500,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6519,19 +6526,19 @@
         <v>78</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="O40" t="s" s="2">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>78</v>
@@ -6580,7 +6587,7 @@
         <v>78</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>79</v>
@@ -6612,10 +6619,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6638,13 +6645,13 @@
         <v>78</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -6671,13 +6678,13 @@
         <v>78</v>
       </c>
       <c r="X41" t="s" s="2">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="Y41" t="s" s="2">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="Z41" t="s" s="2">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="AA41" t="s" s="2">
         <v>78</v>
@@ -6695,7 +6702,7 @@
         <v>78</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>79</v>
@@ -6713,7 +6720,7 @@
         <v>78</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="AM41" t="s" s="2">
         <v>78</v>
@@ -6727,10 +6734,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6753,17 +6760,17 @@
         <v>89</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" t="s" s="2">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>78</v>
@@ -6812,7 +6819,7 @@
         <v>78</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>79</v>
@@ -6844,10 +6851,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6870,16 +6877,16 @@
         <v>78</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
@@ -6929,7 +6936,7 @@
         <v>78</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>79</v>
@@ -6961,10 +6968,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7076,10 +7083,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7193,13 +7200,13 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="C46" t="s" s="2">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="D46" t="s" s="2">
         <v>78</v>
@@ -7221,13 +7228,13 @@
         <v>78</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -7310,10 +7317,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7425,10 +7432,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7540,10 +7547,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7569,13 +7576,13 @@
         <v>102</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
@@ -7583,7 +7590,7 @@
       </c>
       <c r="Q49" s="2"/>
       <c r="R49" t="s" s="2">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="S49" t="s" s="2">
         <v>78</v>
@@ -7625,7 +7632,7 @@
         <v>78</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>88</v>
@@ -7657,10 +7664,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7683,13 +7690,13 @@
         <v>78</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -7740,7 +7747,7 @@
         <v>78</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>79</v>
@@ -7749,7 +7756,7 @@
         <v>88</v>
       </c>
       <c r="AI50" t="s" s="2">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="AJ50" t="s" s="2">
         <v>100</v>
@@ -7772,10 +7779,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7887,10 +7894,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8004,10 +8011,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8030,17 +8037,17 @@
         <v>89</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>78</v>
@@ -8089,7 +8096,7 @@
         <v>78</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>79</v>
@@ -8101,7 +8108,7 @@
         <v>78</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="AK53" t="s" s="2">
         <v>78</v>
@@ -8121,10 +8128,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8236,10 +8243,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8353,10 +8360,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8382,14 +8389,14 @@
         <v>108</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>78</v>
@@ -8417,10 +8424,10 @@
         <v>112</v>
       </c>
       <c r="Y56" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="Z56" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>78</v>
@@ -8438,7 +8445,7 @@
         <v>78</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>79</v>
@@ -8453,7 +8460,7 @@
         <v>100</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="AL56" t="s" s="2">
         <v>78</v>
@@ -8470,10 +8477,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8499,14 +8506,14 @@
         <v>228</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" t="s" s="2">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>78</v>
@@ -8555,7 +8562,7 @@
         <v>78</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>79</v>
@@ -8564,7 +8571,7 @@
         <v>88</v>
       </c>
       <c r="AI57" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="AJ57" t="s" s="2">
         <v>100</v>
@@ -8587,10 +8594,10 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8613,19 +8620,19 @@
         <v>89</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="O58" t="s" s="2">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>78</v>
@@ -8674,7 +8681,7 @@
         <v>78</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>79</v>
@@ -8683,13 +8690,13 @@
         <v>88</v>
       </c>
       <c r="AI58" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="AJ58" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="AL58" t="s" s="2">
         <v>78</v>
@@ -8706,10 +8713,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8732,19 +8739,19 @@
         <v>89</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="O59" t="s" s="2">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>78</v>
@@ -8793,7 +8800,7 @@
         <v>78</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>79</v>
@@ -8802,13 +8809,13 @@
         <v>88</v>
       </c>
       <c r="AI59" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="AJ59" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="AL59" t="s" s="2">
         <v>78</v>
@@ -8825,10 +8832,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8851,17 +8858,17 @@
         <v>89</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>78</v>
@@ -8910,7 +8917,7 @@
         <v>78</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>79</v>
@@ -8942,10 +8949,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9057,10 +9064,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9174,10 +9181,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9203,16 +9210,16 @@
         <v>205</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="O63" t="s" s="2">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>78</v>
@@ -9261,7 +9268,7 @@
         <v>78</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>79</v>
@@ -9293,10 +9300,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9322,14 +9329,14 @@
         <v>259</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" t="s" s="2">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>78</v>
@@ -9378,7 +9385,7 @@
         <v>78</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>79</v>
@@ -9410,10 +9417,10 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9439,10 +9446,10 @@
         <v>108</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
@@ -9472,10 +9479,10 @@
         <v>112</v>
       </c>
       <c r="Y65" t="s" s="2">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="Z65" t="s" s="2">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="AA65" t="s" s="2">
         <v>78</v>
@@ -9493,7 +9500,7 @@
         <v>78</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>79</v>
@@ -9502,33 +9509,33 @@
         <v>88</v>
       </c>
       <c r="AI65" t="s" s="2">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="AJ65" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AK65" t="s" s="2">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="AL65" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="AN65" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AO65" t="s" s="2">
-        <v>459</v>
+        <v>461</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9554,16 +9561,16 @@
         <v>205</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="O66" t="s" s="2">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>78</v>
@@ -9612,7 +9619,7 @@
         <v>78</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>79</v>
@@ -9621,33 +9628,33 @@
         <v>88</v>
       </c>
       <c r="AI66" t="s" s="2">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="AJ66" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AK66" t="s" s="2">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="AL66" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="AN66" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AO66" t="s" s="2">
-        <v>468</v>
+        <v>470</v>
       </c>
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9673,16 +9680,16 @@
         <v>108</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="O67" t="s" s="2">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>78</v>
@@ -9710,10 +9717,10 @@
         <v>112</v>
       </c>
       <c r="Y67" t="s" s="2">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="Z67" t="s" s="2">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="AA67" t="s" s="2">
         <v>78</v>
@@ -9731,7 +9738,7 @@
         <v>78</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>79</v>
@@ -9752,21 +9759,21 @@
         <v>78</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="AN67" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AO67" t="s" s="2">
-        <v>478</v>
+        <v>480</v>
       </c>
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -9789,16 +9796,16 @@
         <v>89</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
@@ -9848,7 +9855,7 @@
         <v>78</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>79</v>
@@ -9880,10 +9887,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -9909,10 +9916,10 @@
         <v>259</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
@@ -9963,7 +9970,7 @@
         <v>78</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>79</v>
@@ -9984,7 +9991,7 @@
         <v>78</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="AN69" t="s" s="2">
         <v>78</v>
@@ -9995,10 +10002,10 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10021,13 +10028,13 @@
         <v>78</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" s="2"/>
@@ -10078,7 +10085,7 @@
         <v>78</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>79</v>
@@ -10093,7 +10100,7 @@
         <v>100</v>
       </c>
       <c r="AK70" t="s" s="2">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="AL70" t="s" s="2">
         <v>78</v>

--- a/branches/feature-careteam/StructureDefinition-riv-care-manager-careteam.xlsx
+++ b/branches/feature-careteam/StructureDefinition-riv-care-manager-careteam.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T12:03:42+00:00</t>
+    <t>2026-10-15T12:49:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1002,7 +1002,7 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-fast-kontakt-typ-kod-eller-text:Typ av fast kontakt ska anges med kod från kodverket Typ av fast kontakt, med text eller med båda. Koder från andra kodverk får inte användas. {(coding.exists() or text.exists()) and coding.all(system = 'https://fhir.inera.se/ig/careteam/CodeSystem/&lt;id&gt;')}</t>
+fast-kontakt-typ-kod-eller-text:Typ av fast kontakt ska anges med kod från kodverket Typ av fast kontakt, med text eller med båda. Koder från andra kodverk får inte användas. {(coding.exists() or text.exists()) and coding.all(system = 'https://terminologitjansten.inera.se/inera-kodverksforvaltning/kodverk/kv_typ_av_fast_kontakt')}</t>
   </si>
   <si>
     <t>Fast kontakt.typ</t>

--- a/branches/feature-careteam/StructureDefinition-riv-care-manager-careteam.xlsx
+++ b/branches/feature-careteam/StructureDefinition-riv-care-manager-careteam.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T12:49:20+00:00</t>
+    <t>2026-10-15T13:32:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -237,7 +237,7 @@
     <t>Constraint(s)</t>
   </si>
   <si>
-    <t>Mapping: Mappning mellan informationsmodell och Fast kontakt</t>
+    <t>Mapping: Informationsmodell - Fast kontakt</t>
   </si>
   <si>
     <t>Mapping: FiveWs Pattern Mapping</t>
@@ -1924,7 +1924,7 @@
     <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="58.43359375" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="40.171875" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="31.65234375" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="39.890625" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="45.140625" customWidth="true" bestFit="true"/>

--- a/branches/feature-careteam/StructureDefinition-riv-care-manager-careteam.xlsx
+++ b/branches/feature-careteam/StructureDefinition-riv-care-manager-careteam.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T13:32:05+00:00</t>
+    <t>2026-10-15T13:47:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/feature-careteam/StructureDefinition-riv-care-manager-careteam.xlsx
+++ b/branches/feature-careteam/StructureDefinition-riv-care-manager-careteam.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T13:47:34+00:00</t>
+    <t>2026-10-15T13:54:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/feature-careteam/StructureDefinition-riv-care-manager-careteam.xlsx
+++ b/branches/feature-careteam/StructureDefinition-riv-care-manager-careteam.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T13:54:27+00:00</t>
+    <t>2026-10-15T14:04:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/feature-careteam/StructureDefinition-riv-care-manager-careteam.xlsx
+++ b/branches/feature-careteam/StructureDefinition-riv-care-manager-careteam.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$70</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$71</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2624" uniqueCount="497">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2663" uniqueCount="505">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T14:04:45+00:00</t>
+    <t>2026-10-28T12:18:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1204,7 +1204,7 @@
     <t>Kontaktvägens tillgänglighet</t>
   </si>
   <si>
-    <t>Anger under vilka veckodagar och tider kontaktvägen är tillgänglig.</t>
+    <t>Value of extension - must be one of a constrained set of the data types (see [Extensibility](http://hl7.org/fhir/R5/extensibility.html) for a list).</t>
   </si>
   <si>
     <t>Extension.value[x]</t>
@@ -1242,6 +1242,9 @@
     <t>Anger återkommande veckodagar och tider då kontaktvägen är tillgänglig.</t>
   </si>
   <si>
+    <t>Saknas veckodagar, tider och period är kontaktvägen tillgänglig alla dagar, hela dygnet, tills vidare.</t>
+  </si>
+  <si>
     <t>A collection of times that the {item} is available.</t>
   </si>
   <si>
@@ -1264,6 +1267,22 @@
     <t>CareTeam.telecom.extension.value[x].availableTime.extension</t>
   </si>
   <si>
+    <t>CareTeam.telecom.extension:availability.value[x].availableTime.extension:period</t>
+  </si>
+  <si>
+    <t>period</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {https://fhir.inera.se/ig/careteam/StructureDefinition/available-time-period}
+</t>
+  </si>
+  <si>
+    <t>Period</t>
+  </si>
+  <si>
+    <t>Datumperiod under vilken veckodagarna och tiderna gäller. Saknas perioden gäller tiderna tills vidare.</t>
+  </si>
+  <si>
     <t>CareTeam.telecom.extension:availability.value[x].availableTime.daysOfWeek</t>
   </si>
   <si>
@@ -1274,6 +1293,9 @@
   </si>
   <si>
     <t>Veckodag då kontaktvägen är tillgänglig.</t>
+  </si>
+  <si>
+    <t>Saknas veckodag gäller tiderna alla dagar i veckan.</t>
   </si>
   <si>
     <t>Indicates which days of the week are available between the start and end Times.</t>
@@ -1329,7 +1351,7 @@
     <t>Tidpunkt då tillgängligheten börjar.</t>
   </si>
   <si>
-    <t>The timezone is expected to be specified or implied by the context this datatype is used.</t>
+    <t>Saknas starttid gäller tillgängligheten från dagens början.</t>
   </si>
   <si>
     <t>The opening time of day. Note: If the AllDay flag is set, then this time is ignored.</t>
@@ -1351,6 +1373,9 @@
   </si>
   <si>
     <t>Tidpunkt då tillgängligheten upphör.</t>
+  </si>
+  <si>
+    <t>Saknas sluttid gäller tillgängligheten till dagens slut.</t>
   </si>
   <si>
     <t>The closing time of day. Note: If the AllDay flag is set, then this time is ignored.</t>
@@ -1886,7 +1911,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AO70"/>
+  <dimension ref="A1:AO71"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="66.8671875" customWidth="true" bestFit="true"/>
@@ -8045,9 +8070,11 @@
       <c r="M53" t="s" s="2">
         <v>389</v>
       </c>
-      <c r="N53" s="2"/>
+      <c r="N53" t="s" s="2">
+        <v>390</v>
+      </c>
       <c r="O53" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>78</v>
@@ -8096,7 +8123,7 @@
         <v>78</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>79</v>
@@ -8108,7 +8135,7 @@
         <v>78</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="AK53" t="s" s="2">
         <v>78</v>
@@ -8128,10 +8155,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8243,10 +8270,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8360,21 +8387,23 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="B56" t="s" s="2">
         <v>397</v>
       </c>
-      <c r="B56" t="s" s="2">
-        <v>398</v>
-      </c>
-      <c r="C56" s="2"/>
+      <c r="C56" t="s" s="2">
+        <v>399</v>
+      </c>
       <c r="D56" t="s" s="2">
         <v>78</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G56" t="s" s="2">
         <v>88</v>
-      </c>
-      <c r="G56" t="s" s="2">
-        <v>80</v>
       </c>
       <c r="H56" t="s" s="2">
         <v>89</v>
@@ -8383,21 +8412,19 @@
         <v>78</v>
       </c>
       <c r="J56" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>108</v>
+        <v>400</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="N56" s="2"/>
-      <c r="O56" t="s" s="2">
-        <v>401</v>
-      </c>
+      <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
         <v>78</v>
       </c>
@@ -8421,13 +8448,13 @@
         <v>78</v>
       </c>
       <c r="X56" t="s" s="2">
-        <v>112</v>
+        <v>78</v>
       </c>
       <c r="Y56" t="s" s="2">
-        <v>402</v>
+        <v>78</v>
       </c>
       <c r="Z56" t="s" s="2">
-        <v>403</v>
+        <v>78</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>78</v>
@@ -8445,7 +8472,7 @@
         <v>78</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>404</v>
+        <v>184</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>79</v>
@@ -8457,10 +8484,10 @@
         <v>78</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>405</v>
+        <v>78</v>
       </c>
       <c r="AL56" t="s" s="2">
         <v>78</v>
@@ -8475,12 +8502,12 @@
         <v>78</v>
       </c>
     </row>
-    <row r="57" hidden="true">
+    <row r="57">
       <c r="A57" t="s" s="2">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8488,13 +8515,13 @@
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H57" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="I57" t="s" s="2">
         <v>78</v>
@@ -8503,17 +8530,19 @@
         <v>89</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>228</v>
+        <v>108</v>
       </c>
       <c r="L57" t="s" s="2">
+        <v>405</v>
+      </c>
+      <c r="M57" t="s" s="2">
+        <v>406</v>
+      </c>
+      <c r="N57" t="s" s="2">
+        <v>407</v>
+      </c>
+      <c r="O57" t="s" s="2">
         <v>408</v>
-      </c>
-      <c r="M57" t="s" s="2">
-        <v>409</v>
-      </c>
-      <c r="N57" s="2"/>
-      <c r="O57" t="s" s="2">
-        <v>410</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>78</v>
@@ -8538,13 +8567,13 @@
         <v>78</v>
       </c>
       <c r="X57" t="s" s="2">
-        <v>78</v>
+        <v>112</v>
       </c>
       <c r="Y57" t="s" s="2">
-        <v>78</v>
+        <v>409</v>
       </c>
       <c r="Z57" t="s" s="2">
-        <v>78</v>
+        <v>410</v>
       </c>
       <c r="AA57" t="s" s="2">
         <v>78</v>
@@ -8568,16 +8597,16 @@
         <v>79</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI57" t="s" s="2">
-        <v>412</v>
+        <v>78</v>
       </c>
       <c r="AJ57" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>78</v>
+        <v>412</v>
       </c>
       <c r="AL57" t="s" s="2">
         <v>78</v>
@@ -8592,7 +8621,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="58">
+    <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
         <v>413</v>
       </c>
@@ -8611,7 +8640,7 @@
         <v>88</v>
       </c>
       <c r="H58" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="I58" t="s" s="2">
         <v>78</v>
@@ -8620,19 +8649,17 @@
         <v>89</v>
       </c>
       <c r="K58" t="s" s="2">
+        <v>228</v>
+      </c>
+      <c r="L58" t="s" s="2">
         <v>415</v>
       </c>
-      <c r="L58" t="s" s="2">
+      <c r="M58" t="s" s="2">
         <v>416</v>
       </c>
-      <c r="M58" t="s" s="2">
+      <c r="N58" s="2"/>
+      <c r="O58" t="s" s="2">
         <v>417</v>
-      </c>
-      <c r="N58" t="s" s="2">
-        <v>418</v>
-      </c>
-      <c r="O58" t="s" s="2">
-        <v>419</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>78</v>
@@ -8681,7 +8708,7 @@
         <v>78</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>79</v>
@@ -8690,13 +8717,13 @@
         <v>88</v>
       </c>
       <c r="AI58" t="s" s="2">
-        <v>412</v>
+        <v>419</v>
       </c>
       <c r="AJ58" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>421</v>
+        <v>78</v>
       </c>
       <c r="AL58" t="s" s="2">
         <v>78</v>
@@ -8713,10 +8740,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8739,16 +8766,16 @@
         <v>89</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>415</v>
+        <v>422</v>
       </c>
       <c r="L59" t="s" s="2">
+        <v>423</v>
+      </c>
+      <c r="M59" t="s" s="2">
         <v>424</v>
       </c>
-      <c r="M59" t="s" s="2">
+      <c r="N59" t="s" s="2">
         <v>425</v>
-      </c>
-      <c r="N59" t="s" s="2">
-        <v>418</v>
       </c>
       <c r="O59" t="s" s="2">
         <v>426</v>
@@ -8809,7 +8836,7 @@
         <v>88</v>
       </c>
       <c r="AI59" t="s" s="2">
-        <v>412</v>
+        <v>419</v>
       </c>
       <c r="AJ59" t="s" s="2">
         <v>100</v>
@@ -8830,7 +8857,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="60" hidden="true">
+    <row r="60">
       <c r="A60" t="s" s="2">
         <v>429</v>
       </c>
@@ -8846,10 +8873,10 @@
         <v>79</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H60" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="I60" t="s" s="2">
         <v>78</v>
@@ -8858,7 +8885,7 @@
         <v>89</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>387</v>
+        <v>422</v>
       </c>
       <c r="L60" t="s" s="2">
         <v>431</v>
@@ -8866,9 +8893,11 @@
       <c r="M60" t="s" s="2">
         <v>432</v>
       </c>
-      <c r="N60" s="2"/>
+      <c r="N60" t="s" s="2">
+        <v>433</v>
+      </c>
       <c r="O60" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>78</v>
@@ -8917,22 +8946,22 @@
         <v>78</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI60" t="s" s="2">
-        <v>78</v>
+        <v>419</v>
       </c>
       <c r="AJ60" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>78</v>
+        <v>436</v>
       </c>
       <c r="AL60" t="s" s="2">
         <v>78</v>
@@ -8949,10 +8978,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8963,7 +8992,7 @@
         <v>79</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H61" t="s" s="2">
         <v>78</v>
@@ -8972,19 +9001,21 @@
         <v>78</v>
       </c>
       <c r="J61" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>205</v>
+        <v>387</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>171</v>
+        <v>439</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>172</v>
+        <v>440</v>
       </c>
       <c r="N61" s="2"/>
-      <c r="O61" s="2"/>
+      <c r="O61" t="s" s="2">
+        <v>441</v>
+      </c>
       <c r="P61" t="s" s="2">
         <v>78</v>
       </c>
@@ -9032,19 +9063,19 @@
         <v>78</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>173</v>
+        <v>442</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH61" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI61" t="s" s="2">
-        <v>174</v>
+        <v>78</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>78</v>
+        <v>100</v>
       </c>
       <c r="AK61" t="s" s="2">
         <v>78</v>
@@ -9053,7 +9084,7 @@
         <v>78</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>175</v>
+        <v>78</v>
       </c>
       <c r="AN61" t="s" s="2">
         <v>78</v>
@@ -9064,21 +9095,21 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>437</v>
+        <v>443</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>438</v>
+        <v>444</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
-        <v>177</v>
+        <v>78</v>
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H62" t="s" s="2">
         <v>78</v>
@@ -9090,17 +9121,15 @@
         <v>78</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>135</v>
+        <v>205</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>179</v>
-      </c>
-      <c r="N62" t="s" s="2">
-        <v>180</v>
-      </c>
+        <v>172</v>
+      </c>
+      <c r="N62" s="2"/>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
         <v>78</v>
@@ -9137,31 +9166,31 @@
         <v>78</v>
       </c>
       <c r="AB62" t="s" s="2">
-        <v>181</v>
+        <v>78</v>
       </c>
       <c r="AC62" t="s" s="2">
-        <v>182</v>
+        <v>78</v>
       </c>
       <c r="AD62" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE62" t="s" s="2">
-        <v>183</v>
+        <v>78</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>184</v>
+        <v>173</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI62" t="s" s="2">
-        <v>78</v>
+        <v>174</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>139</v>
+        <v>78</v>
       </c>
       <c r="AK62" t="s" s="2">
         <v>78</v>
@@ -9181,21 +9210,21 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>439</v>
+        <v>445</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>440</v>
+        <v>446</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
-        <v>78</v>
+        <v>177</v>
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G63" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H63" t="s" s="2">
         <v>78</v>
@@ -9204,23 +9233,21 @@
         <v>78</v>
       </c>
       <c r="J63" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>205</v>
+        <v>135</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>441</v>
+        <v>178</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>442</v>
+        <v>179</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>443</v>
-      </c>
-      <c r="O63" t="s" s="2">
-        <v>444</v>
-      </c>
+        <v>180</v>
+      </c>
+      <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
         <v>78</v>
       </c>
@@ -9256,31 +9283,31 @@
         <v>78</v>
       </c>
       <c r="AB63" t="s" s="2">
-        <v>78</v>
+        <v>181</v>
       </c>
       <c r="AC63" t="s" s="2">
-        <v>78</v>
+        <v>182</v>
       </c>
       <c r="AD63" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE63" t="s" s="2">
-        <v>78</v>
+        <v>183</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>445</v>
+        <v>184</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH63" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI63" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="AK63" t="s" s="2">
         <v>78</v>
@@ -9289,7 +9316,7 @@
         <v>78</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>78</v>
+        <v>175</v>
       </c>
       <c r="AN63" t="s" s="2">
         <v>78</v>
@@ -9300,10 +9327,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9326,17 +9353,19 @@
         <v>89</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>259</v>
+        <v>205</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>449</v>
-      </c>
-      <c r="N64" s="2"/>
+        <v>450</v>
+      </c>
+      <c r="N64" t="s" s="2">
+        <v>451</v>
+      </c>
       <c r="O64" t="s" s="2">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>78</v>
@@ -9385,7 +9414,7 @@
         <v>78</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>79</v>
@@ -9415,12 +9444,12 @@
         <v>78</v>
       </c>
     </row>
-    <row r="65">
+    <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9434,7 +9463,7 @@
         <v>88</v>
       </c>
       <c r="H65" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="I65" t="s" s="2">
         <v>78</v>
@@ -9443,16 +9472,18 @@
         <v>89</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>108</v>
+        <v>259</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c r="N65" s="2"/>
-      <c r="O65" s="2"/>
+      <c r="O65" t="s" s="2">
+        <v>458</v>
+      </c>
       <c r="P65" t="s" s="2">
         <v>78</v>
       </c>
@@ -9476,13 +9507,13 @@
         <v>78</v>
       </c>
       <c r="X65" t="s" s="2">
-        <v>112</v>
+        <v>78</v>
       </c>
       <c r="Y65" t="s" s="2">
-        <v>455</v>
+        <v>78</v>
       </c>
       <c r="Z65" t="s" s="2">
-        <v>456</v>
+        <v>78</v>
       </c>
       <c r="AA65" t="s" s="2">
         <v>78</v>
@@ -9500,7 +9531,7 @@
         <v>78</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>79</v>
@@ -9509,33 +9540,33 @@
         <v>88</v>
       </c>
       <c r="AI65" t="s" s="2">
-        <v>458</v>
+        <v>78</v>
       </c>
       <c r="AJ65" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AK65" t="s" s="2">
-        <v>459</v>
+        <v>78</v>
       </c>
       <c r="AL65" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>460</v>
+        <v>78</v>
       </c>
       <c r="AN65" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AO65" t="s" s="2">
-        <v>461</v>
+        <v>78</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9558,20 +9589,16 @@
         <v>89</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>205</v>
+        <v>108</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>464</v>
-      </c>
-      <c r="N66" t="s" s="2">
-        <v>465</v>
-      </c>
-      <c r="O66" t="s" s="2">
-        <v>466</v>
-      </c>
+        <v>462</v>
+      </c>
+      <c r="N66" s="2"/>
+      <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
         <v>78</v>
       </c>
@@ -9595,13 +9622,13 @@
         <v>78</v>
       </c>
       <c r="X66" t="s" s="2">
-        <v>78</v>
+        <v>112</v>
       </c>
       <c r="Y66" t="s" s="2">
-        <v>78</v>
+        <v>463</v>
       </c>
       <c r="Z66" t="s" s="2">
-        <v>78</v>
+        <v>464</v>
       </c>
       <c r="AA66" t="s" s="2">
         <v>78</v>
@@ -9619,7 +9646,7 @@
         <v>78</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>79</v>
@@ -9628,33 +9655,33 @@
         <v>88</v>
       </c>
       <c r="AI66" t="s" s="2">
-        <v>458</v>
+        <v>466</v>
       </c>
       <c r="AJ66" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AK66" t="s" s="2">
+        <v>467</v>
+      </c>
+      <c r="AL66" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM66" t="s" s="2">
         <v>468</v>
       </c>
-      <c r="AL66" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM66" t="s" s="2">
+      <c r="AN66" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO66" t="s" s="2">
         <v>469</v>
       </c>
-      <c r="AN66" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AO66" t="s" s="2">
+    </row>
+    <row r="67">
+      <c r="A67" t="s" s="2">
         <v>470</v>
       </c>
-    </row>
-    <row r="67" hidden="true">
-      <c r="A67" t="s" s="2">
-        <v>471</v>
-      </c>
       <c r="B67" t="s" s="2">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9668,28 +9695,28 @@
         <v>88</v>
       </c>
       <c r="H67" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="I67" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="J67" t="s" s="2">
         <v>89</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>108</v>
+        <v>205</v>
       </c>
       <c r="L67" t="s" s="2">
+        <v>471</v>
+      </c>
+      <c r="M67" t="s" s="2">
         <v>472</v>
       </c>
-      <c r="M67" t="s" s="2">
+      <c r="N67" t="s" s="2">
         <v>473</v>
       </c>
-      <c r="N67" t="s" s="2">
+      <c r="O67" t="s" s="2">
         <v>474</v>
-      </c>
-      <c r="O67" t="s" s="2">
-        <v>475</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>78</v>
@@ -9714,13 +9741,13 @@
         <v>78</v>
       </c>
       <c r="X67" t="s" s="2">
-        <v>112</v>
+        <v>78</v>
       </c>
       <c r="Y67" t="s" s="2">
-        <v>476</v>
+        <v>78</v>
       </c>
       <c r="Z67" t="s" s="2">
-        <v>477</v>
+        <v>78</v>
       </c>
       <c r="AA67" t="s" s="2">
         <v>78</v>
@@ -9738,7 +9765,7 @@
         <v>78</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>79</v>
@@ -9747,33 +9774,33 @@
         <v>88</v>
       </c>
       <c r="AI67" t="s" s="2">
-        <v>78</v>
+        <v>466</v>
       </c>
       <c r="AJ67" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AK67" t="s" s="2">
-        <v>78</v>
+        <v>476</v>
       </c>
       <c r="AL67" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="AN67" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AO67" t="s" s="2">
-        <v>480</v>
+        <v>478</v>
       </c>
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -9790,24 +9817,26 @@
         <v>78</v>
       </c>
       <c r="I68" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="J68" t="s" s="2">
         <v>89</v>
       </c>
       <c r="K68" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="L68" t="s" s="2">
+        <v>480</v>
+      </c>
+      <c r="M68" t="s" s="2">
+        <v>481</v>
+      </c>
+      <c r="N68" t="s" s="2">
         <v>482</v>
       </c>
-      <c r="L68" t="s" s="2">
+      <c r="O68" t="s" s="2">
         <v>483</v>
       </c>
-      <c r="M68" t="s" s="2">
-        <v>484</v>
-      </c>
-      <c r="N68" t="s" s="2">
-        <v>485</v>
-      </c>
-      <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
         <v>78</v>
       </c>
@@ -9831,13 +9860,13 @@
         <v>78</v>
       </c>
       <c r="X68" t="s" s="2">
-        <v>78</v>
+        <v>112</v>
       </c>
       <c r="Y68" t="s" s="2">
-        <v>78</v>
+        <v>484</v>
       </c>
       <c r="Z68" t="s" s="2">
-        <v>78</v>
+        <v>485</v>
       </c>
       <c r="AA68" t="s" s="2">
         <v>78</v>
@@ -9876,21 +9905,21 @@
         <v>78</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>175</v>
+        <v>487</v>
       </c>
       <c r="AN68" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AO68" t="s" s="2">
-        <v>175</v>
+        <v>488</v>
       </c>
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -9913,15 +9942,17 @@
         <v>89</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>259</v>
+        <v>490</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>489</v>
-      </c>
-      <c r="N69" s="2"/>
+        <v>492</v>
+      </c>
+      <c r="N69" t="s" s="2">
+        <v>493</v>
+      </c>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
         <v>78</v>
@@ -9970,7 +10001,7 @@
         <v>78</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>490</v>
+        <v>494</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>79</v>
@@ -9991,21 +10022,21 @@
         <v>78</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>491</v>
+        <v>175</v>
       </c>
       <c r="AN69" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AO69" t="s" s="2">
-        <v>133</v>
+        <v>175</v>
       </c>
     </row>
-    <row r="70">
+    <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10016,25 +10047,25 @@
         <v>79</v>
       </c>
       <c r="G70" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H70" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I70" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J70" t="s" s="2">
         <v>89</v>
       </c>
-      <c r="I70" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J70" t="s" s="2">
-        <v>78</v>
-      </c>
       <c r="K70" t="s" s="2">
-        <v>493</v>
+        <v>259</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" s="2"/>
@@ -10085,13 +10116,13 @@
         <v>78</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>492</v>
+        <v>498</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH70" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI70" t="s" s="2">
         <v>78</v>
@@ -10100,23 +10131,138 @@
         <v>100</v>
       </c>
       <c r="AK70" t="s" s="2">
-        <v>496</v>
+        <v>78</v>
       </c>
       <c r="AL70" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>78</v>
+        <v>499</v>
       </c>
       <c r="AN70" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AO70" t="s" s="2">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="s" s="2">
+        <v>500</v>
+      </c>
+      <c r="B71" t="s" s="2">
+        <v>500</v>
+      </c>
+      <c r="C71" s="2"/>
+      <c r="D71" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E71" s="2"/>
+      <c r="F71" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H71" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="I71" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J71" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K71" t="s" s="2">
+        <v>501</v>
+      </c>
+      <c r="L71" t="s" s="2">
+        <v>502</v>
+      </c>
+      <c r="M71" t="s" s="2">
+        <v>503</v>
+      </c>
+      <c r="N71" s="2"/>
+      <c r="O71" s="2"/>
+      <c r="P71" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q71" s="2"/>
+      <c r="R71" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S71" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T71" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U71" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V71" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W71" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X71" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y71" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z71" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA71" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB71" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC71" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD71" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE71" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF71" t="s" s="2">
+        <v>500</v>
+      </c>
+      <c r="AG71" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI71" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ71" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK71" t="s" s="2">
+        <v>504</v>
+      </c>
+      <c r="AL71" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM71" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN71" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO71" t="s" s="2">
         <v>78</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AO70">
+  <autoFilter ref="A1:AO71">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -10126,7 +10272,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI69">
+  <conditionalFormatting sqref="A2:AI70">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>
